--- a/biodym_mfa_tool/data/02_output/results_scientific_config.xlsx
+++ b/biodym_mfa_tool/data/02_output/results_scientific_config.xlsx
@@ -37,7 +37,7 @@
     <t>FOMP</t>
   </si>
   <si>
-    <t>data/01_input/250707_Template_CS1.xlsx</t>
+    <t>data/01_input/250714_Template_CS1.xlsx</t>
   </si>
   <si>
     <t>material, WC, DM, CC</t>

--- a/biodym_mfa_tool/data/02_output/results_scientific_config.xlsx
+++ b/biodym_mfa_tool/data/02_output/results_scientific_config.xlsx
@@ -37,7 +37,7 @@
     <t>FOMP</t>
   </si>
   <si>
-    <t>data/01_input/250714_Template_CS1.xlsx</t>
+    <t>data/01_input/250805_Template_CS2.xlsx</t>
   </si>
   <si>
     <t>material, WC, DM, CC</t>

--- a/biodym_mfa_tool/data/02_output/results_scientific_config.xlsx
+++ b/biodym_mfa_tool/data/02_output/results_scientific_config.xlsx
@@ -37,7 +37,7 @@
     <t>FOMP</t>
   </si>
   <si>
-    <t>data/01_input/250805_Template_CS2.xlsx</t>
+    <t>data/01_input/250813_CS1_simple_V1.xlsx</t>
   </si>
   <si>
     <t>material, WC, DM, CC</t>

--- a/biodym_mfa_tool/data/02_output/results_scientific_config.xlsx
+++ b/biodym_mfa_tool/data/02_output/results_scientific_config.xlsx
@@ -37,7 +37,7 @@
     <t>FOMP</t>
   </si>
   <si>
-    <t>data/01_input/250813_CS1_simple_V1.xlsx</t>
+    <t>data/01_input/250831_CS1_simple_V2.xlsx</t>
   </si>
   <si>
     <t>material, WC, DM, CC</t>
